--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_magallanes_y_la_antartica_chilena.xlsx
@@ -404,7 +404,7 @@
         <v>24.17647968539425</v>
       </c>
       <c r="D2">
-        <v>1.688508384160558</v>
+        <v>2.853279541084881</v>
       </c>
       <c r="E2">
         <v>22.01139178154421</v>
@@ -429,7 +429,7 @@
         <v>20.38834951456311</v>
       </c>
       <c r="D3">
-        <v>1.391891891891892</v>
+        <v>1.943396226415094</v>
       </c>
       <c r="E3">
         <v>29.94350282485876</v>
@@ -454,7 +454,7 @@
         <v>8.163265306122449</v>
       </c>
       <c r="D4">
-        <v>3.0625</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="E4">
         <v>18.46153846153846</v>
@@ -479,7 +479,7 @@
         <v>24.47552447552448</v>
       </c>
       <c r="D5">
-        <v>1.588888888888889</v>
+        <v>2.6</v>
       </c>
       <c r="E5">
         <v>23.60515021459228</v>
@@ -504,7 +504,7 @@
         <v>37.50960799385089</v>
       </c>
       <c r="D6">
-        <v>1.880057803468208</v>
+        <v>6.377450980392157</v>
       </c>
       <c r="E6">
         <v>10.23582538886101</v>
@@ -529,7 +529,7 @@
         <v>26.65263157894737</v>
       </c>
       <c r="D7">
-        <v>1.786385859345619</v>
+        <v>3.409906676238335</v>
       </c>
       <c r="E7">
         <v>18.80145768659738</v>
@@ -554,7 +554,7 @@
         <v>35.78595317725753</v>
       </c>
       <c r="D8">
-        <v>1.346846846846847</v>
+        <v>2.6</v>
       </c>
       <c r="E8">
         <v>22.07293666026872</v>
@@ -579,7 +579,7 @@
         <v>31.53153153153153</v>
       </c>
       <c r="D9">
-        <v>1.734375</v>
+        <v>3.827586206896552</v>
       </c>
       <c r="E9">
         <v>16.57142857142857</v>
@@ -604,7 +604,7 @@
         <v>23.86959978796714</v>
       </c>
       <c r="D10">
-        <v>1.811677710554115</v>
+        <v>3.192047377326565</v>
       </c>
       <c r="E10">
         <v>20.18580504132796</v>
@@ -629,7 +629,7 @@
         <v>10.75949367088608</v>
       </c>
       <c r="D11">
-        <v>4.051282051282051</v>
+        <v>7.181818181818182</v>
       </c>
       <c r="E11">
         <v>11.16751269035533</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_magallanes_y_la_antartica_chilena.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.17647968539425</v>
+      </c>
+      <c r="C2">
         <v>35.04738970019663</v>
-      </c>
-      <c r="C2">
-        <v>24.17647968539425</v>
       </c>
       <c r="D2">
         <v>2.853279541084881</v>
       </c>
       <c r="E2">
+        <v>15.18395437737184</v>
+      </c>
+      <c r="F2">
+        <v>62.80465384108395</v>
+      </c>
+      <c r="G2">
         <v>22.01139178154421</v>
-      </c>
-      <c r="F2">
-        <v>62.80465384108396</v>
-      </c>
-      <c r="G2">
-        <v>15.18395437737184</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>20.38834951456311</v>
+      </c>
+      <c r="C3">
         <v>51.45631067961165</v>
-      </c>
-      <c r="C3">
-        <v>20.38834951456311</v>
       </c>
       <c r="D3">
         <v>1.943396226415094</v>
       </c>
       <c r="E3">
-        <v>29.94350282485876</v>
+        <v>11.86440677966102</v>
       </c>
       <c r="F3">
         <v>58.19209039548022</v>
       </c>
       <c r="G3">
-        <v>11.86440677966102</v>
+        <v>29.94350282485876</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="C4">
         <v>24.48979591836735</v>
-      </c>
-      <c r="C4">
-        <v>8.163265306122449</v>
       </c>
       <c r="D4">
         <v>4.083333333333333</v>
       </c>
       <c r="E4">
-        <v>18.46153846153846</v>
+        <v>6.153846153846154</v>
       </c>
       <c r="F4">
         <v>75.38461538461539</v>
       </c>
       <c r="G4">
-        <v>6.153846153846154</v>
+        <v>18.46153846153846</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>24.47552447552448</v>
+      </c>
+      <c r="C5">
         <v>38.46153846153847</v>
-      </c>
-      <c r="C5">
-        <v>24.47552447552448</v>
       </c>
       <c r="D5">
         <v>2.6</v>
       </c>
       <c r="E5">
-        <v>23.60515021459228</v>
+        <v>15.02145922746781</v>
       </c>
       <c r="F5">
         <v>61.37339055793991</v>
       </c>
       <c r="G5">
-        <v>15.02145922746781</v>
+        <v>23.60515021459228</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>37.50960799385089</v>
+      </c>
+      <c r="C6">
         <v>15.68024596464258</v>
-      </c>
-      <c r="C6">
-        <v>37.50960799385089</v>
       </c>
       <c r="D6">
         <v>6.377450980392157</v>
       </c>
       <c r="E6">
-        <v>10.23582538886101</v>
+        <v>24.48569994982439</v>
       </c>
       <c r="F6">
         <v>65.2784746613146</v>
       </c>
       <c r="G6">
-        <v>24.48569994982439</v>
+        <v>10.23582538886101</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.65263157894737</v>
+      </c>
+      <c r="C7">
         <v>29.32631578947368</v>
-      </c>
-      <c r="C7">
-        <v>26.65263157894737</v>
       </c>
       <c r="D7">
         <v>3.409906676238335</v>
       </c>
       <c r="E7">
-        <v>18.80145768659738</v>
+        <v>17.08732622486166</v>
       </c>
       <c r="F7">
         <v>64.11121608854097</v>
       </c>
       <c r="G7">
-        <v>17.08732622486166</v>
+        <v>18.80145768659738</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>35.78595317725753</v>
+      </c>
+      <c r="C8">
         <v>38.46153846153847</v>
-      </c>
-      <c r="C8">
-        <v>35.78595317725753</v>
       </c>
       <c r="D8">
         <v>2.6</v>
       </c>
       <c r="E8">
-        <v>22.07293666026872</v>
+        <v>20.53742802303263</v>
       </c>
       <c r="F8">
         <v>57.38963531669867</v>
       </c>
       <c r="G8">
-        <v>20.53742802303263</v>
+        <v>22.07293666026872</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.53153153153153</v>
+      </c>
+      <c r="C9">
         <v>26.12612612612612</v>
-      </c>
-      <c r="C9">
-        <v>31.53153153153153</v>
       </c>
       <c r="D9">
         <v>3.827586206896552</v>
       </c>
       <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>63.42857142857144</v>
+      </c>
+      <c r="G9">
         <v>16.57142857142857</v>
-      </c>
-      <c r="F9">
-        <v>63.42857142857142</v>
-      </c>
-      <c r="G9">
-        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>23.86959978796714</v>
+      </c>
+      <c r="C10">
         <v>31.32785581765173</v>
-      </c>
-      <c r="C10">
-        <v>23.86959978796714</v>
       </c>
       <c r="D10">
         <v>3.192047377326565</v>
       </c>
       <c r="E10">
-        <v>20.18580504132796</v>
+        <v>15.38014891727577</v>
       </c>
       <c r="F10">
         <v>64.43404604139627</v>
       </c>
       <c r="G10">
-        <v>15.38014891727577</v>
+        <v>20.18580504132796</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>10.75949367088608</v>
+      </c>
+      <c r="C11">
         <v>13.92405063291139</v>
-      </c>
-      <c r="C11">
-        <v>10.75949367088608</v>
       </c>
       <c r="D11">
         <v>7.181818181818182</v>
       </c>
       <c r="E11">
-        <v>11.16751269035533</v>
+        <v>8.629441624365484</v>
       </c>
       <c r="F11">
         <v>80.20304568527919</v>
       </c>
       <c r="G11">
-        <v>8.629441624365484</v>
+        <v>11.16751269035533</v>
       </c>
     </row>
   </sheetData>
